--- a/docs/SPS SMS Commands.xlsx
+++ b/docs/SPS SMS Commands.xlsx
@@ -26,6 +26,7 @@
     <sheet name="SPA Roadmap" sheetId="7" r:id="rId11"/>
     <sheet name="JSON Format" sheetId="10" r:id="rId12"/>
     <sheet name="SPA Display" sheetId="11" r:id="rId13"/>
+    <sheet name="Fuse Detection Alert" sheetId="16" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31055,6 +31056,220 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="110" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SPS Fuse Detection Alert</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Behavior</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Input GPIO</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1.12 / BL54L15 module pad 34; active-low GPIO input.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LED GPIOs</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Utility LED P2.08; cellular LED P2.09.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Circuit</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LTV-814; external 47 kohm pull-up to 3.3 V; 100 nF RC filter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sampling</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Look for an active-low pulse over up to 40 ms, sampling about every 1 ms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wiring assumption</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AC_IN before the fuse; socket metering after the fuse.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trigger</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Input AC present and all socket metering channels below 50 V for three consecutive network-ready alert polls.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alert payload</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alert=Utility power lost - fuse probably blown
+Utility=OFF
+Device=0110
+Outlet=1111
+RSL=-101
+Batt=4.44
+Lat=42.027998
+Lon=-91.631620
+FW=001.00
+HBD=0.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No upstream AC</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Existing Utility power lost alert; no fuse diagnosis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Input AC returns alone</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confirm and send probable fuse alert even during an existing utility outage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Retry and duplicates</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Retry failed sends; send successful fuse alert once until socket voltage returns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Restoration</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Existing Utility power restored alert and outlet report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No outlet report</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The loss/fuse alert is not followed by an outlet report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No new incoming command</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This is an automatic alert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diagnosis limitation</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Metering faults or another downstream interruption can produce the same symptoms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full documentation</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docs/all_cmds.md and docs/sms_commands_client.html</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{707EC4CB-5D5A-4E5D-B024-2AA3920762A0}">
   <dimension ref="A1:F63"/>

--- a/docs/SPS SMS Commands.xlsx
+++ b/docs/SPS SMS Commands.xlsx
@@ -27,6 +27,7 @@
     <sheet name="JSON Format" sheetId="10" r:id="rId12"/>
     <sheet name="SPA Display" sheetId="11" r:id="rId13"/>
     <sheet name="Fuse Detection Alert" sheetId="16" r:id="rId18"/>
+    <sheet name="GetCellularInfo" sheetId="17" r:id="rId19"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31270,6 +31271,235 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B18"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="110" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Command</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">getcellularinfo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Arguments</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None; case-insensitive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Purpose</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read-only, freshly queried cellular diagnostics sent to command sender.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Delivery</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Numbered CellularInfo part N SMS messages; each &lt;=160 characters. Long fields may span parts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Identity</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Model (AT+GMM), ModemFW (AT+CGMR), IMEI, ICCID, IMSI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Network</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carrier, SIM PIN status, CREG, raw CEREG and COPS operator/technology.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Signal</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CSQ raw RSSI index and BER; RSL converted with 2*index-113. CSQ=18,99 maps to RSL=-77.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unknown signal</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CSQ RSSI 99 means unknown; failed query gives -1,-1. Diagnostic RSL=Unknown; legacy status/alerts use -1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radio modes</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Raw CNMP and CMNB. CNMP 38=LTE only; CMNB 1=CAT-M, 2=NB-IoT, 3=both.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Configured APN and fresh raw CNACT context states/IP addresses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Location</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lat and Lon are cached from the normal loop, not freshly queried GPS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Serving cell</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Raw CPSI; radio/system mode, network/cell/band, and LTE RSRQ/RSRP/RSSI/RSSNR when available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unavailable queries</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unavailable for failed/unsupported/empty/oversized diagnostic values; existing getters may show Error or Unknown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Send failure</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remaining parts stop after a failed SMS send. Resend the command to collect a new report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed -77 investigation</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No hardcoded -77 in firmware. Capture CSQ and CPSI from affected hardware to establish why CSQ appears fixed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrections</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unknown CSQ no longer becomes 0 dBm; CPIN parsing errors no longer overwrite RSL; modem model queried rather than hardcoded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Documentation</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all_cmds.md, sms_commands_client.html, Cellular_signal_diagnostics.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Validation</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No project build or hardware test run.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{707EC4CB-5D5A-4E5D-B024-2AA3920762A0}">
   <dimension ref="A1:F63"/>

--- a/docs/SPS SMS Commands.xlsx
+++ b/docs/SPS SMS Commands.xlsx
@@ -31273,7 +31273,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -31307,190 +31307,185 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Purpose</t>
+          <t xml:space="preserve">Delivery</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Read-only, freshly queried cellular diagnostics sent to command sender.</t>
+          <t xml:space="preserve">One SMS, maximum 160 characters; no numbered parts or raw modem commands.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delivery</t>
+          <t xml:space="preserve">Example</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Numbered CellularInfo part N SMS messages; each &lt;=160 characters. Long fields may span parts.</t>
+          <t xml:space="preserve">Cmd=GetCellularInfo
+IMEI=863866074042672
+ICCID=89882280666242663460
+Phone=NONE
+Netw=Roaming
+Carrier=AT&amp;T
+RSL=-63
+APN=iot.1nce.net</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Identity</t>
+          <t xml:space="preserve">IMEI / ICCID</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Model (AT+GMM), ModemFW (AT+CGMR), IMEI, ICCID, IMSI.</t>
+          <t xml:space="preserve">Modem and SIM card identities; limited to 15 and 20 characters.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Network</t>
+          <t xml:space="preserve">Phone</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carrier, SIM PIN status, CREG, raw CEREG and COPS operator/technology.</t>
+          <t xml:space="preserve">NONE: SIM phone number is not currently queried.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Signal</t>
+          <t xml:space="preserve">Netw</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">CSQ raw RSSI index and BER; RSL converted with 2*index-113. CSQ=18,99 maps to RSL=-77.</t>
+          <t xml:space="preserve">Home, Roaming, Searching, Unregistered, Denied, or Unknown.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown signal</t>
+          <t xml:space="preserve">Carrier</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CSQ RSSI 99 means unknown; failed query gives -1,-1. Diagnostic RSL=Unknown; legacy status/alerts use -1.</t>
+          <t xml:space="preserve">Operator name, maximum 24 characters.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Radio modes</t>
+          <t xml:space="preserve">RSL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Raw CNMP and CMNB. CNMP 38=LTE only; CMNB 1=CAT-M, 2=NB-IoT, 3=both.</t>
+          <t xml:space="preserve">Signal estimate in dBm, or Unknown if unavailable.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Data</t>
+          <t xml:space="preserve">APN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Configured APN and fresh raw CNACT context states/IP addresses.</t>
+          <t xml:space="preserve">APN configured in firmware.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Location</t>
+          <t xml:space="preserve">Queries</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lat and Lon are cached from the normal loop, not freshly queried GPS.</t>
+          <t xml:space="preserve">Fresh signal, registration, SIM status, carrier, IMEI and ICCID; network settings are not changed.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Serving cell</t>
+          <t xml:space="preserve">Signal logs</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Raw CPSI; radio/system mode, network/cell/band, and LTE RSRQ/RSRP/RSSI/RSSNR when available.</t>
+          <t xml:space="preserve">INFO: raw signal response and interpreted dBm or unavailable reason, each poll.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unavailable queries</t>
+          <t xml:space="preserve">Registration logs</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unavailable for failed/unsupported/empty/oversized diagnostic values; existing getters may show Error or Unknown.</t>
+          <t xml:space="preserve">INFO: readable registration status and code.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Send failure</t>
+          <t xml:space="preserve">Periodic diagnostics</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remaining parts stop after a failed SMS send. Resend the command to collect a new report.</t>
+          <t xml:space="preserve">LTE registration and serving-cell response logged about every 30 seconds, even while searching.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fixed -77 investigation</t>
+          <t xml:space="preserve">Observed unit</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">No hardcoded -77 in firmware. Capture CSQ and CPSI from affected hardware to establish why CSQ appears fixed.</t>
+          <t xml:space="preserve">Initial searching/unavailable signal changed to AT&amp;T roaming with -63 dBm and an active data context.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrections</t>
+          <t xml:space="preserve">Documentation</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown CSQ no longer becomes 0 dBm; CPIN parsing errors no longer overwrite RSL; modem model queried rather than hardcoded.</t>
+          <t xml:space="preserve">all_cmds.md, sms_commands_client.html, Cellular_signal_diagnostics.md.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Documentation</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">all_cmds.md, sms_commands_client.html, Cellular_signal_diagnostics.md.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
           <t xml:space="preserve">Validation</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t xml:space="preserve">No project build or hardware test run.</t>
         </is>

--- a/docs/SPS SMS Commands.xlsx
+++ b/docs/SPS SMS Commands.xlsx
@@ -31059,7 +31059,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -31267,13 +31267,49 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Diagnostic logs</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>fuse_detection: AC available, freq ~60.00 Hz (pulse 120.00 Hz). Main loop logs changes or roughly every 10 seconds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Frequency estimate</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>GPIO active edges are timed continuously. Average up to eight 6-15 ms intervals, requiring at least three recent intervals. Two half-cycle pulses per mains cycle; divide pulse frequency by two.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Filtered signal</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Steady active input still means AC available. If the RC filter suppresses edges, frequency is unavailable. Frequency is diagnostic only; alert behavior is unchanged.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -31312,7 +31348,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">One SMS, maximum 160 characters; no numbered parts or raw modem commands.</t>
+          <t xml:space="preserve">One SMS, maximum 160 characters; plain names and no raw modem commands.</t>
         </is>
       </c>
     </row>
@@ -31324,170 +31360,195 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cmd=GetCellularInfo
+          <t xml:space="preserve">Cellular
+Carrier=AT&amp;T
+Network=Roaming
+Signal=-63 dBm
+SIM=Ready
 IMEI=863866074042672
 ICCID=89882280666242663460
-Phone=NONE
-Netw=Roaming
-Carrier=AT&amp;T
-RSL=-63
-APN=iot.1nce.net</t>
+Lat=42.056050
+Lon=-91.654126</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">IMEI / ICCID</t>
+          <t xml:space="preserve">Carrier</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modem and SIM card identities; limited to 15 and 20 characters.</t>
+          <t xml:space="preserve">Mobile operator, up to 16 characters.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phone</t>
+          <t xml:space="preserve">Network</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">NONE: SIM phone number is not currently queried.</t>
+          <t xml:space="preserve">Connected, Roaming, Searching, Offline, Denied or Unknown. Connected and Roaming both mean registered.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Netw</t>
+          <t xml:space="preserve">Signal</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Home, Roaming, Searching, Unregistered, Denied, or Unknown.</t>
+          <t xml:space="preserve">Signal estimate in dBm; less negative means stronger. Unknown means no valid reading.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carrier</t>
+          <t xml:space="preserve">SIM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operator name, maximum 24 characters.</t>
+          <t xml:space="preserve">Ready, Locked (PIN/PUK required) or Unknown.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">RSL</t>
+          <t xml:space="preserve">IMEI / ICCID</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Signal estimate in dBm, or Unknown if unavailable.</t>
+          <t xml:space="preserve">Modem and SIM card identities, up to 15 and 20 characters.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">APN</t>
+          <t xml:space="preserve">Lat / Lon</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">APN configured in firmware.</t>
+          <t xml:space="preserve">Always included; cellular estimate in decimal degrees with six decimal places, not a GPS fix.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Queries</t>
+          <t xml:space="preserve">Unavailable location</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fresh signal, registration, SIM status, carrier, IMEI and ICCID; network settings are not changed.</t>
+          <t xml:space="preserve">Unknown. No invented zero position or stale previous position is sent.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Signal logs</t>
+          <t xml:space="preserve">Refresh</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">INFO: raw signal response and interpreted dBm or unavailable reason, each poll.</t>
+          <t xml:space="preserve">Queries registration, signal, SIM status, carrier and identities; requests location when data is connected.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Registration logs</t>
+          <t xml:space="preserve">Location delay</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">INFO: readable registration status and code.</t>
+          <t xml:space="preserve">Location query can take up to 30 seconds. Network settings are not changed.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Periodic diagnostics</t>
+          <t xml:space="preserve">Diagnostics</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">LTE registration and serving-cell response logged about every 30 seconds, even while searching.</t>
+          <t xml:space="preserve">Detailed modem responses and signal interpretation are in INFO logs; see Cellular_signal_diagnostics.md.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Observed unit</t>
+          <t xml:space="preserve">External settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initial searching/unavailable signal changed to AT&amp;T roaming with -63 dBm and an active data context.</t>
+          <t xml:space="preserve">BL54L15 calibration, relay state, alert settings and heartbeat interval use external NOR NVS at 0x400000, size 64 KiB.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Documentation</t>
+          <t xml:space="preserve">OTA reservation</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">all_cmds.md, sms_commands_client.html, Cellular_signal_diagnostics.md.</t>
+          <t xml:space="preserve">Image A at 0x0 (1 MiB), image B at 0x100000 (1 MiB). The freed 2 MiB at 0x200000 is reserved for future growth. Settings stay at 0x400000. OTA is not enabled yet; stored images must fit 1 MiB including metadata.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Validation</t>
+          <t xml:space="preserve">Future data</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">No project build or hardware test run.</t>
+          <t xml:space="preserve">Separate external data area at 0x410000, size 0x3f0000. See External_flash_storage.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Internal storage</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unused; firmware does not mount, migrate or write the old internal settings area. Fresh external storage starts with defaults; reapply needed settings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Storage logs</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Boot logs MX25R6435FZNIL0, JEDEC c2 28 17 and 8 MiB capacity. Each save is read back and compared; logs persisted and verified or an error.</t>
         </is>
       </c>
     </row>

--- a/docs/SPS SMS Commands.xlsx
+++ b/docs/SPS SMS Commands.xlsx
@@ -31309,7 +31309,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -31549,6 +31549,42 @@
       <c r="B19" t="inlineStr">
         <is>
           <t xml:space="preserve">Boot logs MX25R6435FZNIL0, JEDEC c2 28 17 and 8 MiB capacity. Each save is read back and compared; logs persisted and verified or an error.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Relay command errors</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>DeviceOn/DeviceOff return ERR ... GPIO or ERR ... save when switching/persistence fails; outputs may already have changed. Reboot commands report save failures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Repeated relay commands</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Already-correct outputs skip GPIO writes. A mask matching the last loaded/verified saved mask skips flash access; failed saves invalidate that cache.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Relay reset diagnostics</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Boot reset-cause flags plus relay, settings write/readback and SMS-reply stage logs. See Relay_restart_diagnostics.md. Root cause of reported restarts is not yet confirmed.</t>
         </is>
       </c>
     </row>

--- a/docs/SPS SMS Commands.xlsx
+++ b/docs/SPS SMS Commands.xlsx
@@ -28,6 +28,7 @@
     <sheet name="SPA Display" sheetId="11" r:id="rId13"/>
     <sheet name="Fuse Detection Alert" sheetId="16" r:id="rId18"/>
     <sheet name="GetCellularInfo" sheetId="17" r:id="rId19"/>
+    <sheet name="GetHWInfo" sheetId="18" r:id="rId20"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31309,7 +31310,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -31585,6 +31586,206 @@
       <c r="B22" t="inlineStr">
         <is>
           <t>Boot reset-cause flags plus relay, settings write/readback and SMS-reply stage logs. See Relay_restart_diagnostics.md. Root cause of reported restarts is not yet confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Generic SMS retries</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>All command replies, acknowledgements, errors, calibration results, startup/heartbeat reports and alerts use a shared RAM outbox. Failed messages retry after network recovery and the 60-second cooldown. Commands are not re-executed to retry replies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SMS outbox capacity</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>24 messages with owned recipient/payload copies. Incoming commands stay on modem/SIM storage until four reply slots are available. Each accepted part is removed independently; pending RAM messages do not survive reset. Recipient scheduling is fair, with FIFO order per recipient.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Initial connected loads</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>A connected load at startup with its relay already enabled is reported after confirmation. Intentional relay OFF/ON/reboot does not generate load alerts; settle quietly after actual command-driven relay changes. Later load changes on enabled relays still alert. No appliance-specific behavior.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="110" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Command</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gethwinfo; case-insensitive, no arguments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Delivery</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">One SMS, maximum 160 characters. Uses the generic outgoing retry queue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Example</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HW=nRF54L15 FW=001.00
+CPUavg=6.3%
+Up=12345s
+Stack% M=28 L=44 Max=78
+HeapB=2048/4096
+Threads=7 IRQsize=4096B
+Reset=PIN
+SMSQ=2/24</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HW / FW</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Processor and firmware version.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPUavg</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scheduler-measured busy CPU percentage averaged since boot; not instantaneous.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kernel uptime in seconds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stack%</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Peak thread-stack percentages: M=main, L=logging, Max=highest thread. N/A if unavailable. Excludes interrupt-stack usage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeapB</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Newlib malloc-arena used/free bytes. Free is within the acquired arena, not all unused device RAM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Threads / IRQsize</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Observed thread count and configured interrupt-stack capacity in bytes; IRQsize is not measured usage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reset</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Primary recorded boot cause: PIN, SW, WDT, LOCKUP, DEBUG, OTHER, UNCLASS or N/A. Full flags are in RTT logs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SMSQ</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Outgoing messages pending / capacity before this reply is queued.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Relay behavior</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intentional relay OFF/ON/reboot suppresses load alerts caused by those actions. Fresh readings quietly establish post-command state. Load changes on an already-enabled relay still alert; repeating ON on an already-ON relay does not reset monitoring.</t>
         </is>
       </c>
     </row>

--- a/docs/SPS SMS Commands.xlsx
+++ b/docs/SPS SMS Commands.xlsx
@@ -31670,21 +31670,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">HW=nRF54L15 FW=001.00
-CPUavg=6.3%
-Up=12345s
-Stack% M=28 L=44 Max=78
-HeapB=2048/4096
-Threads=7 IRQsize=4096B
-Reset=PIN
-SMSQ=2/24</t>
+          <t xml:space="preserve">nRF54L15 FW=001.00
+CPU avg=3.2%
+Uptime=0d 1h 48m
+Stack peak%=Main:28 Log:44 Max:78
+Heap KiB=2 used/4 free
+Threads=7 Reset=Pin
+SMS queue=2/24</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">HW / FW</t>
+          <t xml:space="preserve">Processor / FW</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -31696,60 +31695,60 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CPUavg</t>
+          <t xml:space="preserve">CPU avg</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduler-measured busy CPU percentage averaged since boot; not instantaneous.</t>
+          <t xml:space="preserve">Busy CPU percentage averaged since boot; not instantaneous.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Up</t>
+          <t xml:space="preserve">Uptime</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kernel uptime in seconds.</t>
+          <t xml:space="preserve">Time since boot in days, hours and minutes.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stack%</t>
+          <t xml:space="preserve">Stack peak%</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Peak thread-stack percentages: M=main, L=logging, Max=highest thread. N/A if unavailable. Excludes interrupt-stack usage.</t>
+          <t xml:space="preserve">Peak usage since boot: Main=application, Log=logging, Max=highest thread percentage. Lower means more stack headroom. N/A if unavailable. Detailed interrupt-stack readings stay in RTT logs.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeapB</t>
+          <t xml:space="preserve">Heap KiB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Newlib malloc-arena used/free bytes. Free is within the acquired arena, not all unused device RAM.</t>
+          <t xml:space="preserve">Newlib malloc-arena used/free memory in whole KiB (1024 bytes), rounded down. Free is within the acquired arena, not total unused RAM.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Threads / IRQsize</t>
+          <t xml:space="preserve">Threads</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Observed thread count and configured interrupt-stack capacity in bytes; IRQsize is not measured usage.</t>
+          <t xml:space="preserve">Observed number of operating-system threads.</t>
         </is>
       </c>
     </row>
@@ -31761,14 +31760,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Primary recorded boot cause: PIN, SW, WDT, LOCKUP, DEBUG, OTHER, UNCLASS or N/A. Full flags are in RTT logs.</t>
+          <t xml:space="preserve">Primary recorded boot cause: Pin, Software, Watchdog, Lockup, Debug, Other, Unknown (no classified cause) or N/A. Full flags remain in RTT logs.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">SMSQ</t>
+          <t xml:space="preserve">SMS queue</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">

--- a/docs/SPS SMS Commands.xlsx
+++ b/docs/SPS SMS Commands.xlsx
@@ -29,6 +29,7 @@
     <sheet name="Fuse Detection Alert" sheetId="16" r:id="rId18"/>
     <sheet name="GetCellularInfo" sheetId="17" r:id="rId19"/>
     <sheet name="GetHWInfo" sheetId="18" r:id="rId20"/>
+    <sheet name="GetOTAInfo" sheetId="19" r:id="rId21"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31792,6 +31793,172 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="110" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Command</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">getotainfo; case-insensitive, no arguments. One SMS, max 160 characters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Example</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OTA
+Run=Internal
+From=Backup B
+Backup=Ready
+Health=OK/60s
+Boots=12 WDT=3
+Streak=0/3
+Recoveries=1
+Last=Watchdog
+Update=Idle</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Run / From</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Run is always Internal. From: Initial=first observed image; Updated=different OTA/SWD image; Backup B=restored from B; Unknown=unavailable. Origin survives reboots until image changes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Backup</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ready=header/length/CRC readback pass now; None=not provisioned; Bad=failed verification. MCUboot authenticates signatures at install.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Health</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wait/60s or OK/60s; one minute for testing after completed main-loop progress with settings and verified backup. Production can use 300000U.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Boots / WDT</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Persistent application handoffs (including first start/power cycles) and total hardware or Zephyr task-watchdog resets. Recovery housekeeping reboots excluded from Boots. Tracking starts with updated MCUboot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Streak</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Current consecutive watchdog failure count / 3. Cleared by healthy check or non-watchdog restart.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recoveries / Last</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Completed restorations and latest completed reason: Watchdog, Image (boot/validation failure), None. History survives healthy check and normal reboot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Update</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Idle, Download, Pending or Recovery. This query never starts an update.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Persistence</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Separate external NVS history record, original policy/settings ABI unchanged. Counts are diagnostic; saturation at 32-bit maximum, not an atomic power-event audit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compatibility</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Install updated MCUboot and application. A restored older image without this command cannot answer it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Errors</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OTA info unavailable; check boot journal logs. Non-MCUboot builds: OTA not enabled in this firmware.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{707EC4CB-5D5A-4E5D-B024-2AA3920762A0}">
   <dimension ref="A1:F63"/>

--- a/docs/SPS SMS Commands.xlsx
+++ b/docs/SPS SMS Commands.xlsx
@@ -30,6 +30,7 @@
     <sheet name="GetCellularInfo" sheetId="17" r:id="rId19"/>
     <sheet name="GetHWInfo" sheetId="18" r:id="rId20"/>
     <sheet name="GetOTAInfo" sheetId="19" r:id="rId21"/>
+    <sheet name="OTA Update" sheetId="20" r:id="rId22"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31168,7 +31169,7 @@
 Batt=4.44
 Lat=42.027998
 Lon=-91.631620
-FW=001.00
+FW=1.0.0+0
 HBD=0.000</t>
         </is>
       </c>
@@ -31671,7 +31672,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">nRF54L15 FW=001.00
+          <t xml:space="preserve">nRF54L15 FW=1.0.0+0
 CPU avg=3.2%
 Uptime=0d 1h 48m
 Stack peak%=Main:28 Log:44 Max:78
@@ -31915,7 +31916,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idle, Download, Pending or Recovery. This query never starts an update.</t>
+          <t xml:space="preserve">Idle, Checking, Manifest, Download, Stage, Verify, Pending, Failed or Recovery. This query never starts an update.</t>
         </is>
       </c>
     </row>
@@ -31952,6 +31953,199 @@
       <c r="B12" t="inlineStr">
         <is>
           <t xml:space="preserve">OTA info unavailable; check boot journal logs. Non-MCUboot builds: OTA not enabled in this firmware.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="110" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Command</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ota=1.0.1 or ota=1.0.1+2; case-insensitive. Without +build, build 0 is requested.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Version</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FW now reports the signed MCUboot version from root VERSION, e.g. 1.0.0+0. Increment VERSION before each release. Requested version must match manifest and binary. The running version is rejected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acceptance reply</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OTA 1.0.1+0 accepted; checking manifest</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Completion reply</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OTA 1.0.1+0 verified; rebooting to install</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failures</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ERR OTA &lt;version&gt;: &lt;step&gt; (&lt;code&gt;). Download/verification failure does not request reboot. Missing URL: ERR OTA URL not configured.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prerequisites</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Matching MCUboot/partition layout/signing key installed; current image Health=OK/60s; registered modem/data; configured HTTPS base URL; sufficient modem filesystem space. One update at a time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Publish</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Upload dfu_application/manifest.json and smart_power_socket.signed.bin from the same current dfu_application.zip. Do not upload merged.hex, unsigned binary or the ZIP as the firmware file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prepare folder</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">python tools/verify_ota_build.py build-ota refreshes build-ota/dfu_application/ after build checks. Named binary equals zephyr.signed.bin; manifest bytes unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Repository URL</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONFIG_SPS_OTA_BASE_URL uses raw.githubusercontent.com/haseebzaib/REPO/main/dfu_application/. REPO is a placeholder; default empty. Use HTTPS 200 direct file URLs, no redirects/private repositories.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Checks</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manifest target/version/size/filename; actual image header/version; exact lengths; flash CRC/SHA-256 readback; Ed25519 signature before arming. MCUboot independently authenticates before install.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Slots</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Run=Internal. A=download/install staging. B=previous known-good recovery copy. Current healthy internal image is archived to B before reusing A. Roles do not alternate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SMS and reboot</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wait for modem acceptance of this request's completion SMS, with generic retries, before rebooting. This is not proof of recipient delivery. Pending can wait through send failures; another reset may install the armed image.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">getotainfo Update: Idle, Checking, Manifest, Download, Stage, Verify, Pending, Failed, Recovery. Failure returns Idle after its error reply is queued.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recovery</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Existing lifetime recovery restores B after three consecutive watchdog failures. Failed transfers do not erase settings. BLE transport remains future work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Limits / testing</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30-minute deadline per download; image &lt;=0xfc000 bytes and modem free space. HTTPS carrier/repository test remains to be performed. TLS certificate provisioning depends on modem profile; see docs/HTTP_OTA.md.</t>
         </is>
       </c>
     </row>

--- a/docs/SPS SMS Commands.xlsx
+++ b/docs/SPS SMS Commands.xlsx
@@ -31169,7 +31169,7 @@
 Batt=4.44
 Lat=42.027998
 Lon=-91.631620
-FW=1.0.0+0
+FW=1.0.1+0
 HBD=0.000</t>
         </is>
       </c>
@@ -31672,7 +31672,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">nRF54L15 FW=1.0.0+0
+          <t xml:space="preserve">nRF54L15 FW=1.0.1+0
 CPU avg=3.2%
 Uptime=0d 1h 48m
 Stack peak%=Main:28 Log:44 Max:78
@@ -31796,7 +31796,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -31824,6 +31824,7 @@
       <c r="B2" t="inlineStr">
         <is>
           <t xml:space="preserve">OTA
+FW=1.0.1+0
 Run=Internal
 From=Backup B
 Backup=Ready
@@ -31956,13 +31957,37 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Firmware version</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>FW reports the running image version, e.g. 1.0.1+0, from root VERSION. Verify after update or rollback. It is not the server manifest/staged version.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Long version/counters</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Full version and exact counters remain within one SMS using compact labels when needed: Run=Int, B=Backup, Rec=Recoveries, Upd=Update.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -32073,7 +32098,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONFIG_SPS_OTA_BASE_URL uses raw.githubusercontent.com/haseebzaib/REPO/main/dfu_application/. REPO is a placeholder; default empty. Use HTTPS 200 direct file URLs, no redirects/private repositories.</t>
+          <t xml:space="preserve">BL54L15 CONFIG_SPS_OTA_BASE_URL is https://raw.githubusercontent.com/haseebzaib/SPS_OTA_UPDATE/main/dfu_application/. Upload manifest.json and its named signed binary there. Generic Kconfig default is empty. Use HTTPS 200 direct file URLs, no redirects/private repositories.</t>
         </is>
       </c>
     </row>
@@ -32145,7 +32170,55 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">30-minute deadline per download; image &lt;=0xfc000 bytes and modem free space. HTTPS carrier/repository test remains to be performed. TLS certificate provisioning depends on modem profile; see docs/HTTP_OTA.md.</t>
+          <t xml:space="preserve">30-minute overall deadline; 3 minutes without increasing byte progress; 10-second grace for idle without HTTP result. Third consecutive failed status query aborts. Image &lt;=0xfc000 bytes and modem free space. Carrier/repository HTTPS testing remains; see HTTP_OTA.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Modem recovery</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Native idle is checked before deleting a destination. Cleanup handles transfers left across MCU resets or a lost start-command OK. PDP deactivation is asynchronous; later starts must still prove native idle. File sessions resynchronize after a failed close. Completion URCs take priority over overlapping query errors; duplicate results cannot replace the first result.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Version file</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Root VERSION: PATCHLEVEL=1 gives 1.0.1+0; PATCHLEVEL=2 gives 1.0.2+0. Rebuild and publish the generated pair. Do not edit manifest version or signed binary by hand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Signing key / machines</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Current test builds use the SDK example root-ed25519.pem. It is not regenerated per build. Both machines must match the client bootloader public key. Run python tools/ota_key_info.py build-ota on each. See OTA_signing_and_releases.md for project-owned keys.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Initial test</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SWD flash build-swd-1.0.0/merged.hex first; wait for Health=OK/60s; send ota=1.0.1; after install check getotainfo FW=1.0.1+0. Do not SWD flash 1.0.1 first if testing an upgrade to that same version.</t>
         </is>
       </c>
     </row>

--- a/docs/SPS SMS Commands.xlsx
+++ b/docs/SPS SMS Commands.xlsx
@@ -32086,7 +32086,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">python tools/verify_ota_build.py build-ota refreshes build-ota/dfu_application/ after build checks. Named binary equals zephyr.signed.bin; manifest bytes unchanged.</t>
+          <t xml:space="preserve">Normal sysbuild automatically refreshes &lt;build-dir&gt;/dfu_application/ after the ZIP and checks source/compiled/signed/manifest versions agree. The explicit verify_ota_build.py command adds full signature/partition checks. Named binary equals zephyr.signed.bin; manifest bytes unchanged.</t>
         </is>
       </c>
     </row>

--- a/docs/SPS SMS Commands.xlsx
+++ b/docs/SPS SMS Commands.xlsx
@@ -31857,7 +31857,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ready=header/length/CRC readback pass now; None=not provisioned; Bad=failed verification. MCUboot authenticates signatures at install.</t>
+          <t xml:space="preserve">Ready means header/length/CRC and signature against either project public key pass a fresh readback. None=not provisioned, Bad=verification failed. The first healthy run reprovisions an intact B signed outside the new trust set after the SWD transition.</t>
         </is>
       </c>
     </row>
@@ -31987,7 +31987,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -32206,7 +32206,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Current test builds use the SDK example root-ed25519.pem. It is not regenerated per build. Both machines must match the client bootloader public key. Run python tools/ota_key_info.py build-ota on each. See OTA_signing_and_releases.md for project-owned keys.</t>
+          <t>Two permanent project pairs: keys/ota/private/primary-ed25519.pem (default) and recovery-ed25519.pem (alternate). Public PEMs under keys/ota/public are embedded in MCUboot and app. Both machines use the same key files. Missing/untrusted private files fail the build. Compare python tools/ota_key_info.py &lt;build-dir&gt;.</t>
         </is>
       </c>
     </row>
@@ -32218,7 +32218,43 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SWD flash build-swd-1.0.0/merged.hex first; wait for Health=OK/60s; send ota=1.0.1; after install check getotainfo FW=1.0.1+0. Do not SWD flash 1.0.1 first if testing an upgrade to that same version.</t>
+          <t>Install the new project-key build-ota/merged.hex once via SWD, wait Health=OK/60s and Backup=Ready, then increment VERSION, build/sign using either project key and publish the DFU pair. Old SDK-signed 1.0.0/1.0.1 artifacts are not compatible with the new trust anchors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Progress messages</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>OTA &lt;version&gt;: Downloading firmware...; Downloading firmware: 25%; Download complete; saving firmware...; Saving firmware: 75%; Firmware saved; checking signature...</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Progress timing</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Stage changes plus current percentage when crossing 25% boundaries, at least 30 seconds apart, or about once per minute for long phases. Slow manifest fetches report checking release information. Pauses report waiting for download data. Fast transfers can skip intermediate values; pending HTTP completion never claims 100%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Progress queue policy</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Sent only to command sender. At most one optional notice stays queued, leaving five free slots after insertion. Old unsent stages are superseded. Terminal success/error cancels remaining optional progress and keeps the essential result/reboot SMS ID independent. Already submitted messages cannot be recalled. Other replies/alerts keep normal retries.</t>
         </is>
       </c>
     </row>

--- a/docs/SPS SMS Commands.xlsx
+++ b/docs/SPS SMS Commands.xlsx
@@ -31828,7 +31828,7 @@
 Run=Internal
 From=Backup B
 Backup=Ready
-Health=OK/60s
+Health=Off
 Boots=12 WDT=3
 Streak=0/3
 Recoveries=1
@@ -31857,7 +31857,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ready means header/length/CRC and signature against either project public key pass a fresh readback. None=not provisioned, Bad=verification failed. The first healthy run reprovisions an intact B signed outside the new trust set after the SWD transition.</t>
+          <t xml:space="preserve">Ready means header/length/CRC and signature against either project public key pass a fresh readback. None=not provisioned, Bad=verification failed. Startup backup provisioning is disabled. Update preparation authenticates and archives the running image to B before erasing A, replacing an old SDK-signed backup then.</t>
         </is>
       </c>
     </row>
@@ -31869,7 +31869,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wait/60s or OK/60s; one minute for testing after completed main-loop progress with settings and verified backup. Production can use 300000U.</t>
+          <t xml:space="preserve">Off: startup health check disabled (CONFIG_SPS_OTA_HEALTH_CHECK=n). OTA has no 60-second health prerequisite. Backup creation and signature checks remain mandatory during update preparation.</t>
         </is>
       </c>
     </row>
@@ -31893,7 +31893,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Current consecutive watchdog failure count / 3. Cleared by healthy check or non-watchdog restart.</t>
+          <t xml:space="preserve">Current consecutive watchdog failure count / 3. Cleared after one minute of sustained main-loop progress or a non-watchdog restart, independently of the disabled OTA health check.</t>
         </is>
       </c>
     </row>
@@ -31905,7 +31905,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Completed restorations and latest completed reason: Watchdog, Image (boot/validation failure), None. History survives healthy check and normal reboot.</t>
+          <t xml:space="preserve">Completed restorations and latest completed reason: Watchdog, Image (boot/validation failure), None. History survives watchdog streak clearing and normal reboot.</t>
         </is>
       </c>
     </row>
@@ -32062,7 +32062,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matching MCUboot/partition layout/signing key installed; current image Health=OK/60s; registered modem/data; configured HTTPS base URL; sufficient modem filesystem space. One update at a time.</t>
+          <t xml:space="preserve">Matching MCUboot/partition layout/signing key installed; startup health check disabled (Health=Off), no health wait; registered modem/data; configured HTTPS base URL; sufficient modem filesystem space. One update at a time.</t>
         </is>
       </c>
     </row>
@@ -32218,7 +32218,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Install the new project-key build-ota/merged.hex once via SWD, wait Health=OK/60s and Backup=Ready, then increment VERSION, build/sign using either project key and publish the DFU pair. Old SDK-signed 1.0.0/1.0.1 artifacts are not compatible with the new trust anchors.</t>
+          <t>Install the new project-key build-ota/merged.hex once via SWD, confirm Health=Off (no startup health wait), then increment VERSION, build/sign using either project key and publish the DFU pair. Old SDK-signed 1.0.0/1.0.1 artifacts are not compatible with the new trust anchors.</t>
         </is>
       </c>
     </row>

--- a/docs/SPS SMS Commands.xlsx
+++ b/docs/SPS SMS Commands.xlsx
@@ -31987,7 +31987,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -32255,6 +32255,42 @@
       <c r="B22" t="inlineStr">
         <is>
           <t>Sent only to command sender. At most one optional notice stays queued, leaving five free slots after insertion. Old unsent stages are superseded. Terminal success/error cancels remaining optional progress and keeps the essential result/reboot SMS ID independent. Already submitted messages cannot be recalled. Other replies/alerts keep normal retries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Modem busy recovery</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>A stale download is cancelled with PDP deactivation and checked for native idle for 10 seconds. If still active or unqueryable, one modem reset is attempted; AT readiness is checked for up to 60 seconds, normal APN/radio/SMS settings are restored, and HTTP idle is verified before file reuse. Queued SMS replies remain in RAM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Setup recovery notice</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Recovering modem connection; please wait... . An accepted job waits up to three minutes for modem/network recovery. Persistent recovery failure stops the job without repeated modem resets or restarting the MCU. Failed transfers are not silently replayed; retry OTA after recovery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>MCU startup HTTP cleanup</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Every MCU startup checks native HTTP state once after AT readiness/configuration. A stale or unknown HTTP state schedules cancellation/recovery without an OTA command; an idle modem is not reset. Normal modem polling and SMS submission wait until recovery completes.</t>
         </is>
       </c>
     </row>

--- a/docs/SPS SMS Commands.xlsx
+++ b/docs/SPS SMS Commands.xlsx
@@ -31987,7 +31987,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -32291,6 +32291,18 @@
       <c r="B25" t="inlineStr">
         <is>
           <t>Every MCU startup checks native HTTP state once after AT readiness/configuration. A stale or unknown HTTP state schedules cancellation/recovery without an OTA command; an idle modem is not reset. Normal modem polling and SMS submission wait until recovery completes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Storage phase and timing</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Saving firmware includes creating/reusing backup B, erasing staging A, modem-to-flash transfer and verification. Aligned image erases now use up to 64 KiB requests. Copy uses 1 KiB frames in batches up to 32 frames, checking a three-second budget between frames. OTA timing logs separate backup, staging erase, modem reads, flash writes, other copy work and verification. SMS times include cellular delays; speed improvements apply once the optimized updater is running.</t>
         </is>
       </c>
     </row>
